--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261020.xlsx
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,363,197</t>
+          <t>27,387,560</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>27,387,560</t>
+          <t>1,363,197</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
